--- a/assessment_forms/023_process_evaluation_checklist--assessment_forms.xlsx
+++ b/assessment_forms/023_process_evaluation_checklist--assessment_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,9 +431,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,15 +510,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>process_evaluation_checklist_form_section_1</t>
+          <t>introduction_and_background</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Process Evaluation Checklist</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction and Background</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Provide details about the process</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -533,15 +537,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>process_evaluation_checklist_form_section_2</t>
+          <t>process_overview</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Process Evaluation Checklist</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Process Overview</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Describe the process</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -556,15 +564,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>process_evaluation_checklist_form_section_3</t>
+          <t>current_process</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Process Evaluation Checklist</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Current Process</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe the current process</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -579,15 +591,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>process_evaluation_checklist_form_section_4</t>
+          <t>challenges_bottlenecks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Process Evaluation Checklist</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Challenges and Bottlenecks</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Identify any challenges or bottlenecks</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -602,15 +618,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>process_evaluation_checklist_form_section_5</t>
+          <t>opportunities_for_improvement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Process Evaluation Checklist</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Opportunities for Improvement</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Suggest improvements</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -625,15 +645,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>process_evaluation_checklist_form_section_6</t>
+          <t>metrics_monitoring</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Process Evaluation Checklist</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Metrics and Monitoring</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Describe current metrics and monitoring</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -648,15 +672,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>process_evaluation_checklist_form_section_7</t>
+          <t>risk_management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Process Evaluation Checklist</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Risk Management</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Identify and mitigate risks</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -671,15 +699,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>process_evaluation_checklist_form_section_8</t>
+          <t>communication_feedback</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Process Evaluation Checklist</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Communication and Feedback</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Describe communication and feedback</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -694,15 +726,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>process_evaluation_checklist_form_section_9</t>
+          <t>continuous_improvement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Process Evaluation Checklist</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Continuous Improvement</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Suggest improvements</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -717,15 +753,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>process_evaluation_checklist_form_section_10</t>
+          <t>conclusion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Process Evaluation Checklist</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Final thoughts</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
